--- a/GBU_EN8180_Zuordnung.xlsx
+++ b/GBU_EN8180_Zuordnung.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lesehinweise" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Zuordnung'!$A$1:$L$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Zuordnung'!$A$1:$L$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,14 +486,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
@@ -506,32 +506,32 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nr.</t>
+          <t>Nr. 2019</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Abschnitt EN 81-80</t>
+          <t>Nr. 2003</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Gefährdungssituation (Kurzbezeichnung)</t>
+          <t>Gruppe</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Prüfpunkt (Kurzbezeichnung)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Priorität</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Risikoprofil A.1</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Zeitplan A.2</t>
+          <t>Zeitplan</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -566,42 +566,44 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5.1.4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Schädliche Stoffe an der Anlage (z. B. Asbest in Bremsbelägen, Löschkammern, Verkleidungen)</t>
+          <t>Allgemeines</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Hoch</t>
+          <t>Zugänglichkeit für Personen mit eingeschränkter Mobilität (EN 81-82)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>I/C-D</t>
+          <t>nicht eingestuft</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Kurzfristig</t>
+          <t>Kein Zeitplan; der Punkt verweist auf eine eigene Norm der Reihe EN 81</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>MF-U01</t>
+          <t>MF-K10</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Asbesthaltige oder andere schädliche Baustoffe im Bereich der Anlage</t>
+          <t>Eingeschränkte Zugänglichkeit für Personen mit eingeschränkter Mobilität</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -609,47 +611,53 @@
           <t>voll</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>In der Prüfliste ohne Prioritätsstufe: der Punkt verweist auf eine eigene Norm der Reihe EN 81.</t>
+        </is>
+      </c>
       <c r="K2" s="3" t="n"/>
       <c r="L2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
-        <v>2</v>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>5.2.1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Zugänglichkeit für Personen mit eingeschränkter Mobilität</t>
+          <t>Allgemeines</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>Widerstand gegen mutwillige Zerstörung (CEN/TS 81-83)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>nicht eingestuft</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Nach Risikobeurteilung im Einzelfall (5.1.5)</t>
+          <t>Kein Zeitplan; der Punkt verweist auf eine eigene Norm der Reihe EN 81</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>MF-K10</t>
+          <t>MF-K11</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Eingeschränkte Zugänglichkeit für Personen mit eingeschränkter Mobilität</t>
+          <t>Beschädigte Fahrkorbausstattung / Vandalismus</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -659,203 +667,215 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>In A.1 nicht risikoprofiliert (besondere Anforderung nach 5.1.5).</t>
+          <t>In der Prüfliste ohne Prioritätsstufe: der Punkt verweist auf eine eigene Norm der Reihe EN 81.</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>5.2.2</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Anhalte- und Nachregulierungsgenauigkeit</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Hoch</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>I/C-D, II/C</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Kurzfristig</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>MF-K03</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Unzureichende Haltegenauigkeit / Stufenbildung an den Haltestellen</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>voll</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>neu 2019</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Allgemeines</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Feuerwehraufzug (EN 81-72)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>nicht eingestuft</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Kein Zeitplan; der Punkt verweist auf eine eigene Norm der Reihe EN 81</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>MF-SF01</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Feuerwehraufzug / gebäudeseitige Sonderfunktionen nicht nachgewiesen</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>teilweise</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>MF-SF01 erhebt die gebäudeseitige Sonderfunktion Feuerwehraufzug; die Bauartanforderungen nach EN 81-72 selbst sind nicht Gegenstand des MF-Fragebogens.</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>4</v>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Widerstand gegen mutwillige Zerstörung (Vandalismus)</t>
+          <t>Allgemeines</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>Verhalten des Aufzugs im Brandfall (EN 81-73)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
           <t>nicht eingestuft</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Nach Risikobeurteilung im Einzelfall (5.1.5)</t>
+          <t>Kein Zeitplan; der Punkt verweist auf eine eigene Norm der Reihe EN 81</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>MF-K11</t>
+          <t>MF-K08, MF-K09, MF-U09</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Beschädigte Fahrkorbausstattung / Vandalismus</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>voll</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>In A.1 nicht risikoprofiliert (besondere Anforderung nach 5.1.5).</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Verhalten und Überwachungsfunktionen im Brandfall</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>nicht eingestuft</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Nach Risikobeurteilung im Einzelfall (5.1.5)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>MF-K08, MF-K09, MF-U09</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Fehlende Brandfallsteuerung trotz Anforderung im Brandschutzkonzept
 Fehlender Hinweis „Aufzug im Brandfall nicht benutzen"
 Brandmeldeanlage, Brandfall- und Evakuierungssteuerung nicht abgestimmt</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>voll</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>In A.1 nicht risikoprofiliert (besondere Anforderung nach 5.1.5).</t>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>In der Prüfliste ohne Prioritätsstufe: der Punkt verweist auf eine eigene Norm der Reihe EN 81.</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>neu 2019</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Allgemeines</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Erdbebensicherheit (EN 81-77)</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>nicht eingestuft</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Kein Zeitplan; der Punkt verweist auf eine eigene Norm der Reihe EN 81</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Erdbebensicherheit (EN 81-77) wird im MF-Fragebogen nicht erhoben.</t>
         </is>
       </c>
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>6</v>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>5.5.1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Durchbrochene (nicht geschlossene) Schachtumwehrung</t>
+          <t>Allgemeines</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Extrem</t>
+          <t>Anlage frei von schädlichen Stoffen (z. B. Asbest)</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>I/B</t>
+          <t>Hoch</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Sofort, Aufzug muss stillgelegt werden</t>
+          <t>Kurzfristig</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>MF-S03</t>
+          <t>MF-U01</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Unzureichende Schachtumwehrung oder Schachtwände</t>
+          <t>Asbesthaltige oder andere schädliche Baustoffe im Bereich der Anlage</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -868,29 +888,31 @@
       <c r="L7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>5.5.1.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Teilumwehrter Schacht mit zu niedriger Umwehrung</t>
+          <t>Schacht</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>Schließeinrichtungen an Zugangs-, Notfall- und Inspektionstüren zu Schacht und Schachtgrube</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>I/C-D</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -898,12 +920,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>MF-S03</t>
+          <t>MF-S07, MF-G04</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Unzureichende Schachtumwehrung oder Schachtwände</t>
+          <t>Zugänge zum Schacht und zugehörige Schalteinrichtungen nicht frei und sicher begehbar
+Unsicherer Zugang zur Schachtgrube (Leiter, Grubenzugangstür)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -916,27 +939,29 @@
       <c r="L8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>8</v>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>5.5.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Schließeinrichtungen an Zugangstüren zu Schacht und Schachtgrube</t>
+          <t>Schacht</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>Anhalten des Fahrkorbs bei geöffneten Zugangs-, Notfall- und Inspektionstüren</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
           <t>Hoch</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>I/C-D</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -965,29 +990,31 @@
       <c r="L9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>5.5.3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Senkrechte Fläche unterhalb der Schachttürschwelle</t>
+          <t>Schacht</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>Vollwandige Schachtumwehrung</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>II/C</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -995,12 +1022,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>MF-T07</t>
+          <t>MF-S03</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Unzureichende Fläche unterhalb der Schachttürschwelle</t>
+          <t>Unzureichende Schachtumwehrung oder Schachtwände</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,99 +1035,104 @@
           <t>voll</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Ergänzt 04.09.2026 (EN 81-20 5.2.5.3.2).</t>
-        </is>
-      </c>
+      <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>5.5.4</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Betretbarer Raum unter dem Schacht ohne Fangvorrichtung am Gegengewicht</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Mittel</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>I/D-E</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>MF-G07</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Fehlende oder unzulängliche Abtrennung und Sicherung des Gegengewichts</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>voll</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Schacht</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Zugang zu den Verriegelungseinrichtungen der Schachttür bei durchbrochener Umwehrung</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Kurzfristig</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>MF-S03, MF-T01</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Unzureichende Schachtumwehrung oder Schachtwände
+Unsichere Verriegelung der Schachttüren</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>teilweise</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Nr. 33 (2003): MF erhebt Umwehrung und Verriegelung getrennt, nicht ihren Abstand zueinander.</t>
+        </is>
+      </c>
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>5.5.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Abtrennung der Fahrbahn des Gegengewichts/Ausgleichsgewichts</t>
+          <t>Schacht</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Mittel</t>
+          <t>Teilumwehrter Schacht</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>I/D-E</t>
+          <t>Hoch</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
+          <t>Kurzfristig</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>MF-G07</t>
+          <t>MF-S03</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Fehlende oder unzulängliche Abtrennung und Sicherung des Gegengewichts</t>
+          <t>Unzureichende Schachtumwehrung oder Schachtwände</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1113,29 +1145,31 @@
       <c r="L12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>12</v>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>5.5.6.1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Abtrennung in der Schachtgrube bei mehreren Aufzügen im selben Schacht</t>
+          <t>Schacht</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
+          <t>Höhe der senkrechten Fläche unterhalb der Schachttürschwelle</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>I/C-D</t>
-        </is>
-      </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -1143,12 +1177,12 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>MF-G08</t>
+          <t>MF-T07</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Fehlende Abtrennung zum Nachbaraufzug in der Schachtgrube</t>
+          <t>Unzureichende Fläche unterhalb der Schachttürschwelle</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1156,48 +1190,53 @@
           <t>voll</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Nr. 9 (2003): Ergänzt 04.09.2026 (EN 81-20 5.2.5.3.2).</t>
+        </is>
+      </c>
       <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>5.5.6.2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Abtrennung über die Schachthöhe bei mehreren Aufzügen im selben Schacht</t>
+          <t>Schacht</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Hoch</t>
+          <t>Schutz der Zugangsbereiche unter dem Schacht (Fangvorrichtung am Gegengewicht)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>I/C-D</t>
+          <t>Niedrig</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Kurzfristig</t>
+          <t>Langfristig oder im Rahmen einer Modernisierung der betroffenen Komponente</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>MF-F03, MF-G08</t>
+          <t>MF-G07</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Gefährdung durch Nachbaraufzug oder dessen Gegengewicht (Fahrkorbdach)
-Fehlende Abtrennung zum Nachbaraufzug in der Schachtgrube</t>
+          <t>Fehlende oder unzulängliche Abtrennung und Sicherung des Gegengewichts</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1210,43 +1249,44 @@
       <c r="L14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>14</v>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>5.5.7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Schutzräume in Schachtkopf und Schachtgrube</t>
+          <t>Schacht</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Hoch</t>
+          <t>Abtrennung der Fahrbahn des Gegen- oder Ausgleichsgewichts</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>I/C-D</t>
+          <t>Niedrig</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Kurzfristig</t>
+          <t>Langfristig oder im Rahmen einer Modernisierung der betroffenen Komponente</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>MF-F04, MF-G02</t>
+          <t>MF-G07</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Unzureichender Schutzraum / Kopffreiheit im Schachtkopf
-Unzureichender Schutzraum in der Schachtgrube</t>
+          <t>Fehlende oder unzulängliche Abtrennung und Sicherung des Gegengewichts</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1259,29 +1299,31 @@
       <c r="L15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>5.5.8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Sicherer Zugang zur Schachtgrube</t>
+          <t>Schacht</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Abtrennung in der Schachtgrube bei mehreren Aufzügen im selben Schacht</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>II/C</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -1289,12 +1331,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>MF-G04</t>
+          <t>MF-G08</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Unsicherer Zugang zur Schachtgrube (Leiter, Grubenzugangstür)</t>
+          <t>Fehlende Abtrennung zum Nachbaraufzug in der Schachtgrube</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1307,29 +1349,31 @@
       <c r="L16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>16</v>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>5.5.9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Not-Halt in Schachtgrube und Rollenraum</t>
+          <t>Schacht</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
+          <t>Abtrennung beweglicher Teile über die volle Höhe bei gemeinsam genutztem Schacht</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>I/C-D</t>
-        </is>
-      </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -1337,13 +1381,13 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>MF-G03, MF-M20</t>
+          <t>MF-F03, MF-G08</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Fehlender Not-Halt oder fehlende Inspektionssteuerung in der Schachtgrube
-Fehlender Not-Halt im zusätzlichen Rollenraum</t>
+          <t>Gefährdung durch Nachbaraufzug oder dessen Gegengewicht (Fahrkorbdach)
+Fehlende Abtrennung zum Nachbaraufzug in der Schachtgrube</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1356,29 +1400,31 @@
       <c r="L17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>5.5.10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Schachtbeleuchtung</t>
+          <t>Schacht</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Schutzräume und Freiräume im Schachtkopf</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>I/C-D, II/C</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -1386,13 +1432,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>MF-S01, MF-G01</t>
+          <t>MF-F04, MF-G02</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Unzureichende Schachtbeleuchtung
-Unzureichende Beleuchtung in der Schachtgrube</t>
+          <t>Unzureichender Schutzraum / Kopffreiheit im Schachtkopf
+Unzureichender Schutzraum in der Schachtgrube</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1405,29 +1451,31 @@
       <c r="L18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>18</v>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>5.5.11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Notruf in Schachtgrube und auf dem Fahrkorbdach</t>
+          <t>Schacht</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
+          <t>Schutzräume und Freiräume in der Schachtgrube</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>II/C-D</t>
-        </is>
-      </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -1435,13 +1483,13 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>MF-G05, MF-F09</t>
+          <t>MF-F04, MF-G02</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Keine Selbstbefreiung aus der Schachtgrube und kein Notruf in der Grube
-Fehlender Notruf auf dem Fahrkorbdach</t>
+          <t>Unzureichender Schutzraum / Kopffreiheit im Schachtkopf
+Unzureichender Schutzraum in der Schachtgrube</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1454,29 +1502,31 @@
       <c r="L19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>5.6.1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Zugänge zum Triebwerks- oder Rollenraum</t>
+          <t>Schacht</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>Maßnahmen für den Zugang zur Schachtgrube</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>II/C</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -1484,394 +1534,412 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
+          <t>MF-G04</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Unsicherer Zugang zur Schachtgrube (Leiter, Grubenzugangstür)</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Schacht</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Schachtbeleuchtung</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Kurzfristig</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>MF-S01, MF-G01</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Unzureichende Schachtbeleuchtung
+Unzureichende Beleuchtung in der Schachtgrube</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Schacht</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Notbremsschalter in der Schachtgrube</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Kurzfristig</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>MF-G03, MF-M20</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Fehlender Not-Halt oder fehlende Inspektionssteuerung in der Schachtgrube
+Fehlender Not-Halt im zusätzlichen Rollenraum</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="3" t="n"/>
+      <c r="L22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Schacht</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Notrufauslöseeinrichtungen in der Schachtgrube und auf dem Fahrkorbdach</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Mittel</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>MF-G05, MF-F09</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Keine Selbstbefreiung aus der Schachtgrube und kein Notruf in der Grube
+Fehlender Notruf auf dem Fahrkorbdach</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Schacht</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Horizontaler Abstand zwischen innerer Schachtwand und Türschwelle bzw. Türrahmen des Fahrkorbs</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Kurzfristig</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>MF-F01</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Fehlende oder unzureichende Absturzsicherung auf dem Fahrkorbdach</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>teilweise</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Nr. 58 (2003): MF erhebt den Abstand an der Fahrkorbdachkante (Absturzsicherung).</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Schacht</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Horizontaler Abstand zwischen geschlossener Fahrkorbtür und Schachttür</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Kurzfristig</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>MF-K05</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Zu großer Abstand zwischen Fahrkorbschwelle und Schachtwand</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr"/>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>neu 2019</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Schacht</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Abstand zwischen den Führungskanten von Fahrkorbtür und Schachttür</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Kurzfristig</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Wird nicht erhoben; MF-K05 erfasst den Abstand Fahrkorbschwelle/Schachtwand, nicht den Abstand der Führungskanten.</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="n"/>
+      <c r="L26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Betriebsräume und Rollenräume</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Zugänge zu den Aufstellungsorten von Triebwerks- und Rollenraum</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Kurzfristig</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
           <t>MF-Z03, MF-Z07, MF-Z02</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>Unsicherer Aufstieg (Treppe, Leiter) zum Triebwerksraum
 Fehlende oder unzureichende Zugangstür zum Triebwerks-/Maschinenraum
 Unsicherer Verkehrsweg zum Triebwerks-/Steuerungsraum (Rutschen, Stolpern, Enge)</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>voll</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="3" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>5.6.2</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Rutschiger Boden im Triebwerks- oder Rollenraum</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Mittel</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>II/D</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>MF-M06</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Rutschiger, verschmutzter oder ölverunreinigter Boden im Triebwerksraum</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>voll</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr"/>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="3" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>5.6.3</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Abstände und Freiflächen im Triebwerksraum</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Hoch</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>II/C-D</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Kurzfristig</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>MF-M04</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Unzureichende Raumhöhe, Bewegungs- und Freiflächen im Triebwerksraum</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>voll</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="3" t="n"/>
-      <c r="L22" s="3" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>5.6.4</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Unterschiedliche Ebenen im Triebwerks- oder Rollenraum</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Hoch</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>II/C</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Kurzfristig</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>MF-M05</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Unterschiedliche Ebenen, Podeste und Bodenöffnungen im Triebwerksraum ungesichert</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>voll</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>5.6.5</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Beleuchtung im Triebwerks- oder Rollenraum</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Hoch</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>II/C</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Kurzfristig</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>MF-M01</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Unzureichende Beleuchtung im Triebwerks-/Maschinenraum</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>voll</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>5.6.6</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Hebezeuge und Anschlagpunkte</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Hoch</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>I/D-E, II/C-D</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Kurzfristig</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>MF-M14</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Fehlende oder unzureichende Hebezeuge / Anschlagpunkte im Triebwerksraum</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>voll</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr"/>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>5.7.1</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Durchbrochene Schacht- und Fahrkorbtüren (Gittertüren)</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Extrem</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>I/B</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Sofort, Aufzug muss stillgelegt werden</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>MF-T04, MF-T06</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>Ungeeignetes Glas oder fehlender Einzugsschutz an Türen mit Glas
-Fahrkorb ohne Abschlusstür oder ohne Schließkantensicherung</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>teilweise</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>MF erhebt Glaseinsätze und den Fahrkorbabschluss; Gittertüren nur über Scherengitter/Lichtgitter.</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>5.7.2</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Ausführung der Schachttürbefestigungen</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Hoch</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>I/C-D</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Kurzfristig</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>MF-T08</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Türblatt kann aus der Führung fallen (fehlende Rückhalteeinrichtung)</t>
-        </is>
-      </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
           <t>voll</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>Ergänzt 04.09.2026 (EN 81-20 5.3.5.3.2 Rückhalteeinrichtungen).</t>
-        </is>
-      </c>
+      <c r="J27" s="4" t="inlineStr"/>
       <c r="K27" s="3" t="n"/>
       <c r="L27" s="3" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>5.7.3</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Geeignetes Glas in Schachttüren</t>
+          <t>Betriebsräume und Rollenräume</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Beleuchtung in den Betriebsräumen und Rollenräumen</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>I/C-D, II/C</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -1879,12 +1947,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>MF-T04</t>
+          <t>MF-M01</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Ungeeignetes Glas oder fehlender Einzugsschutz an Türen mit Glas</t>
+          <t>Unzureichende Beleuchtung im Triebwerks-/Maschinenraum</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1897,42 +1965,45 @@
       <c r="L28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>28</v>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>5.7.4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Schutz gegen Einziehen von Fingern an Glas-Schiebetüren</t>
+          <t>Betriebsräume und Rollenräume</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Mittel</t>
+          <t>Notbremsschalter in Rollenräumen</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>III/C-D</t>
+          <t>Hoch</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
+          <t>Kurzfristig</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>MF-T04</t>
+          <t>MF-G03, MF-M20</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Ungeeignetes Glas oder fehlender Einzugsschutz an Türen mit Glas</t>
+          <t>Fehlender Not-Halt oder fehlende Inspektionssteuerung in der Schachtgrube
+Fehlender Not-Halt im zusätzlichen Rollenraum</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -1945,29 +2016,31 @@
       <c r="L29" s="3" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>5.7.5</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Beleuchtung an den Schachtzugängen</t>
+          <t>Betriebsräume und Rollenräume</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>Aufhängepunkte für die Handhabung von Einrichtungen in Betriebsräumen und oben im Schacht</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>Mittel</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>III/C</t>
-        </is>
-      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
@@ -1975,12 +2048,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>MF-S02</t>
+          <t>MF-M14</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Unzureichende Beleuchtung an den Schachtzugängen</t>
+          <t>Fehlende oder unzureichende Hebezeuge / Anschlagpunkte im Triebwerksraum</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1993,42 +2066,44 @@
       <c r="L30" s="3" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
-        <v>30</v>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>5.7.6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Schutzeinrichtungen an kraftbetätigten Türen (Schließkantensicherung)</t>
+          <t>Betriebsräume und Rollenräume</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Extrem</t>
+          <t>Rutschhemmender Boden an den Aufstellungsorten von Triebwerks- und Rollenraum</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>I/B, III/A</t>
+          <t>Niedrig</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Sofort, Aufzug muss stillgelegt werden</t>
+          <t>Langfristig oder im Rahmen einer Modernisierung der betroffenen Komponente</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>MF-T06</t>
+          <t>MF-M06</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Fahrkorb ohne Abschlusstür oder ohne Schließkantensicherung</t>
+          <t>Rutschiger, verschmutzter oder ölverunreinigter Boden im Triebwerksraum</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -2041,42 +2116,44 @@
       <c r="L31" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>5.7.7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Verriegelungseinrichtung der Schachttür</t>
+          <t>Betriebsräume und Rollenräume</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Hoch</t>
+          <t>Horizontale und vertikale Freiräume in den Betriebsräumen für sicheres Arbeiten</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>I/C-D</t>
+          <t>Mittel</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Kurzfristig</t>
+          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>MF-T01</t>
+          <t>MF-M04</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Unsichere Verriegelung der Schachttüren</t>
+          <t>Unzureichende Raumhöhe, Bewegungs- und Freiflächen im Triebwerksraum</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2089,29 +2166,31 @@
       <c r="L32" s="3" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
-        <v>32</v>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>5.7.8.1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Notentriegelung der Schachttür nur mit besonderem Werkzeug</t>
+          <t>Betriebsräume und Rollenräume</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
+          <t>Arbeitsebenen und Vertiefungen im Triebwerksraum</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>I/C-D</t>
-        </is>
-      </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -2119,12 +2198,12 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>MF-T02</t>
+          <t>MF-M05</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Fehlende oder schlecht erreichbare Notentriegelung der Schachttüren</t>
+          <t>Unterschiedliche Ebenen, Podeste und Bodenöffnungen im Triebwerksraum ungesichert</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -2137,182 +2216,191 @@
       <c r="L33" s="3" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>5.7.8.2</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Durchbrochene Schachtwand in der Nähe der Türverriegelung</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Hoch</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>I/D</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>Kurzfristig</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>MF-S03, MF-T01</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>Unzureichende Schachtumwehrung oder Schachtwände
-Unsichere Verriegelung der Schachttüren</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>teilweise</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>MF erhebt Umwehrung und Verriegelung getrennt, nicht ihren Abstand zueinander.</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Betriebsräume und Rollenräume</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Gegensprechanlage zwischen Fahrkorb und Ort des Notbetriebs</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Mittel</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>MF-M18</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Fehlende oder unzulängliche Sprechverbindung zwischen Fahrkorb und Triebwerksraum</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="3" t="n"/>
       <c r="L34" s="3" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>5.7.9</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Selbstschließen der Schachttüren (Sperrmittel)</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Schachttüren und Fahrkorbtüren</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Vollwandige Schachttüren</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>I/D</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>MF-T03</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>Schachttüren nicht selbstschließend</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>voll</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>MF-T04, MF-T06</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Ungeeignetes Glas oder fehlender Einzugsschutz an Türen mit Glas
+Fahrkorb ohne Abschlusstür oder ohne Schließkantensicherung</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>teilweise</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>Nr. 25 (2003): MF erhebt Glaseinsätze und den Fahrkorbabschluss; Gittertüren nur über Scherengitter/Lichtgitter.</t>
+        </is>
+      </c>
       <c r="K35" s="3" t="n"/>
       <c r="L35" s="3" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>5.7.10</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Verbindung zwischen den Türblättern mehrteiliger Schachttüren</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Schachttüren und Fahrkorbtüren</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Vollwandige Fahrkorbtüren</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>I/D</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>MF-T09</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Unzureichende Verbindung der Türblätter mehrteiliger Schachttüren</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>voll</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Ergänzt 04.09.2026 (EN 81-20 5.3.11).</t>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>MF-T04, MF-T06</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Ungeeignetes Glas oder fehlender Einzugsschutz an Türen mit Glas
+Fahrkorb ohne Abschlusstür oder ohne Schließkantensicherung</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>teilweise</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Nr. 25 (2003): MF erhebt Glaseinsätze und den Fahrkorbabschluss; Gittertüren nur über Scherengitter/Lichtgitter.</t>
         </is>
       </c>
       <c r="K36" s="3" t="n"/>
       <c r="L36" s="3" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
-        <v>36</v>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>5.7.11</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Feuerwiderstandsfähigkeit der Schachttüren</t>
+          <t>Schachttüren und Fahrkorbtüren</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
+          <t>Festigkeit von Schachttüren</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>I/D</t>
-        </is>
-      </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -2320,12 +2408,12 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>MF-T05</t>
+          <t>MF-T08</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Unzureichende Feuerwiderstandsfähigkeit der Schachttüren</t>
+          <t>Türblatt kann aus der Führung fallen (fehlende Rückhalteeinrichtung)</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2333,99 +2421,107 @@
           <t>voll</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr"/>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Nr. 26 (2003): Ergänzt 04.09.2026 (EN 81-20 5.3.5.3.2 Rückhalteeinrichtungen).</t>
+        </is>
+      </c>
       <c r="K37" s="3" t="n"/>
       <c r="L37" s="3" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>5.7.12</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Fahrkorbtür bewegt sich bei geöffneter Schachttür</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Hoch</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>III/B</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Kurzfristig</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>MF-K05</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Zu großer Abstand zwischen Fahrkorbschwelle und Schachtwand</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>voll</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>Über die Fahrkorbtür-Verriegelung außerhalb der Entriegelungszone.</t>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>neu 2019</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Schachttüren und Fahrkorbtüren</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Festigkeit von Fahrkorbtüren</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Mittel</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>Festigkeit der Fahrkorbtüren wird nicht erhoben; MF-T02/T04 betreffen die Schachttüren.</t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
-        <v>38</v>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>5.8.1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Verhältnis von Nutzfläche zur Nennlast</t>
+          <t>Schachttüren und Fahrkorbtüren</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Mittel</t>
+          <t>Glas in den Schachttüren außer Schauöffnungen</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>II/D</t>
+          <t>Hoch</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
+          <t>Kurzfristig</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>MF-K06</t>
+          <t>MF-T04</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Fehlende Kennzeichnung der Nennlast, unpassende Nutzfläche oder fehlende Überlastkontrolle</t>
+          <t>Ungeeignetes Glas oder fehlender Einzugsschutz an Türen mit Glas</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2438,29 +2534,31 @@
       <c r="L39" s="3" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>39</v>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>5.8.2</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Länge der Fahrkorbtürschürze</t>
+          <t>Schachttüren und Fahrkorbtüren</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>Glas in den Fahrkorbtüren außer Schauöffnungen</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>I/D</t>
-        </is>
-      </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -2468,12 +2566,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>MF-K04</t>
+          <t>MF-T04</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Unzureichende Fahrkorbtürschürze</t>
+          <t>Ungeeignetes Glas oder fehlender Einzugsschutz an Türen mit Glas</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2486,29 +2584,31 @@
       <c r="L40" s="3" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
-        <v>40</v>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>5.8.3</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Fahrkorb ohne Abschlusstür</t>
+          <t>Schachttüren und Fahrkorbtüren</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
+          <t>Glasschauöffnungen in den Schachttüren</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>I/D, II/C</t>
-        </is>
-      </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -2516,12 +2616,12 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>MF-T06</t>
+          <t>MF-T04</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Fahrkorb ohne Abschlusstür oder ohne Schließkantensicherung</t>
+          <t>Ungeeignetes Glas oder fehlender Einzugsschutz an Türen mit Glas</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2534,29 +2634,31 @@
       <c r="L41" s="3" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>41</v>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>5.8.4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Verriegelung und Überwachung der Klappe im Fahrkorbdach</t>
+          <t>Schachttüren und Fahrkorbtüren</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>Glasschauöffnungen in den Fahrkorbtüren</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>II/C-D</t>
-        </is>
-      </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -2564,12 +2666,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>MF-F07</t>
+          <t>MF-T04</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Nicht tragfähiges Fahrkorbdach oder unüberwachte Dachklappe</t>
+          <t>Ungeeignetes Glas oder fehlender Einzugsschutz an Türen mit Glas</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2582,42 +2684,44 @@
       <c r="L42" s="3" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
-        <v>42</v>
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>5.8.5</t>
+          <t>30b</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Festigkeit des Fahrkorbdachs</t>
+          <t>Schachttüren und Fahrkorbtüren</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Mittel</t>
+          <t>Nichttrennende Schutzeinrichtung (z. B. Lichtschranke) an kraftbetätigten Türen</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>III/C-D</t>
+          <t>Hoch</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
+          <t>Kurzfristig</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>MF-F07</t>
+          <t>MF-T06</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Nicht tragfähiges Fahrkorbdach oder unüberwachte Dachklappe</t>
+          <t>Fahrkorb ohne Abschlusstür oder ohne Schließkantensicherung</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2630,29 +2734,31 @@
       <c r="L43" s="3" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>43</v>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>5.8.6</t>
+          <t>30a</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Umwehrung (Geländer) auf dem Fahrkorbdach</t>
+          <t>Schachttüren und Fahrkorbtüren</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>Begrenzung des Kraftaufwands beim Schließen kraftbetätigter Schiebetüren (150 N)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>I/D</t>
-        </is>
-      </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -2660,12 +2766,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>MF-F01</t>
+          <t>MF-T06</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Fehlende oder unzureichende Absturzsicherung auf dem Fahrkorbdach</t>
+          <t>Fahrkorb ohne Abschlusstür oder ohne Schließkantensicherung</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2678,77 +2784,85 @@
       <c r="L44" s="3" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>5.8.7</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Lüftung des Fahrkorbs</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>neu 2019</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Schachttüren und Fahrkorbtüren</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Begrenzung des Kraftaufwands (150 N) beim Schließen anderer als automatisch kraftbetätigter Schiebetüren</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>II/C-D</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>MF-K07</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>Unzureichende Lüftung des Fahrkorbs</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>voll</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr"/>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Kraftbegrenzung an anderen als automatisch kraftbetätigten Schiebetüren wird nicht erhoben.</t>
+        </is>
+      </c>
       <c r="K45" s="3" t="n"/>
       <c r="L45" s="3" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>45</v>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>5.8.8.1</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Beleuchtung im Fahrkorb (Normalbetrieb)</t>
+          <t>Schachttüren und Fahrkorbtüren</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>Schutz gegen das Einziehen von Kinderhänden bei waagerecht bewegten Glastüren</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
           <t>Mittel</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>III/C</t>
-        </is>
-      </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
@@ -2756,12 +2870,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>MF-K15</t>
+          <t>MF-T04</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Unzureichende Beleuchtung im Fahrkorb (Normalbetrieb)</t>
+          <t>Ungeeignetes Glas oder fehlender Einzugsschutz an Türen mit Glas</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2769,51 +2883,49 @@
           <t>voll</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>Ergänzt 04.09.2026 (EN 81-20 5.4.10.1 bis 5.4.10.3: mind. 100 Lux an den Befehlsgebern und 1 m über dem Boden bis 100 mm an die Wände).</t>
-        </is>
-      </c>
+      <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
-        <v>46</v>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>5.8.8.2</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Notbeleuchtung im Fahrkorb</t>
+          <t>Schachttüren und Fahrkorbtüren</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Hoch</t>
+          <t>Beleuchtung der Ladestellen in der Nähe der Schachttüren</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>III/B</t>
+          <t>Mittel</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Kurzfristig</t>
+          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>MF-K02</t>
+          <t>MF-S02</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Fehlende oder unzulängliche Notbeleuchtung im Fahrkorb</t>
+          <t>Unzureichende Beleuchtung an den Schachtzugängen</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2826,29 +2938,31 @@
       <c r="L47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>47</v>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>5.9.1</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Schutz an Treibscheiben, Rollen und Kettenrädern gegen Verletzungen</t>
+          <t>Schachttüren und Fahrkorbtüren</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>Schachttürverriegelungen</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>II/C-D</t>
-        </is>
-      </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -2856,12 +2970,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>MF-M03</t>
+          <t>MF-T01</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Fehlender oder unzureichender Schutz an drehenden Teilen (Treibscheibe, Umlenkrollen, Begrenzer)</t>
+          <t>Unsichere Verriegelung der Schachttüren</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2874,29 +2988,31 @@
       <c r="L48" s="3" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
-        <v>48</v>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>5.9.1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Schutz gegen Herausspringen von Seilen oder Ketten</t>
+          <t>Schachttüren und Fahrkorbtüren</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
+          <t>Notentriegelung der Schachttüren nur mit besonderen Mitteln (z. B. Dreikantschlüssel)</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>II/C-D</t>
-        </is>
-      </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -2904,12 +3020,12 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>MF-M03</t>
+          <t>MF-T02</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Fehlender oder unzureichender Schutz an drehenden Teilen (Treibscheibe, Umlenkrollen, Begrenzer)</t>
+          <t>Fehlende oder schlecht erreichbare Notentriegelung der Schachttüren</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -2922,42 +3038,44 @@
       <c r="L49" s="3" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>49</v>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>5.9.1</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Schutz gegen Eindringen von Fremdkörpern in Treibscheibe und Rollen</t>
+          <t>Schachttüren und Fahrkorbtüren</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Mittel</t>
+          <t>Selbsttätiges Schließen und Verriegeln einer geöffneten Schachttür bei Fahrkorb außerhalb der Entriegelungszone</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>III/C-D</t>
+          <t>Hoch</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
+          <t>Kurzfristig</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>MF-M03</t>
+          <t>MF-T03</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Fehlender oder unzureichender Schutz an drehenden Teilen (Treibscheibe, Umlenkrollen, Begrenzer)</t>
+          <t>Schachttüren nicht selbstschließend</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2970,42 +3088,44 @@
       <c r="L50" s="3" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
-        <v>50</v>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>5.9.2</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Fangvorrichtung und Geschwindigkeitsbegrenzer bei elektrisch angetriebenen Aufzügen</t>
+          <t>Schachttüren und Fahrkorbtüren</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Hoch</t>
+          <t>Schachtschiebetüren mit mehreren Türblättern: Verbindung und elektrische Prüfung der geschlossenen Position</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>I/D, II/C</t>
+          <t>Mittel</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Kurzfristig</t>
+          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>MF-S05</t>
+          <t>MF-T09</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Fehlende oder ungeprüfte Fangvorrichtung, Geschwindigkeitsbegrenzer oder Schlaffseilsicherung</t>
+          <t>Unzureichende Verbindung der Türblätter mehrteiliger Schachttüren</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -3013,47 +3133,53 @@
           <t>voll</t>
         </is>
       </c>
-      <c r="J51" s="4" t="inlineStr"/>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>Nr. 35 (2003): Ergänzt 04.09.2026 (EN 81-20 5.3.11).</t>
+        </is>
+      </c>
       <c r="K51" s="3" t="n"/>
       <c r="L51" s="3" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>51</v>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>4.18</t>
+        </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>5.9.3</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Schlaffseilschalter am Begrenzerseil (Spanngewicht)</t>
+          <t>Schachttüren und Fahrkorbtüren</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Hoch</t>
+          <t>Feuerwiderstand von Schachttüren</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>I/D</t>
+          <t>Mittel</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Kurzfristig</t>
+          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>MF-S05</t>
+          <t>MF-T05</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Fehlende oder ungeprüfte Fangvorrichtung, Geschwindigkeitsbegrenzer oder Schlaffseilsicherung</t>
+          <t>Unzureichende Feuerwiderstandsfähigkeit der Schachttüren</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -3066,42 +3192,44 @@
       <c r="L52" s="3" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n">
-        <v>52</v>
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>5.9.4</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Schutz gegen unkontrollierte Aufwärtsbewegung des Fahrkorbs</t>
+          <t>Schachttüren und Fahrkorbtüren</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Hoch</t>
+          <t>Kraftbetriebene Fahrkorb-Schiebetür bewegt sich erst nach dem Schließen der Schachtdrehtür</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>I/D, II/C-D</t>
+          <t>Mittel</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Kurzfristig</t>
+          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>MF-K13</t>
+          <t>MF-K05</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Fehlender Schutz gegen Übergeschwindigkeit aufwärts / Sturz nach oben</t>
+          <t>Zu großer Abstand zwischen Fahrkorbschwelle und Schachtwand</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -3109,34 +3237,40 @@
           <t>voll</t>
         </is>
       </c>
-      <c r="J53" s="4" t="inlineStr"/>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>Nr. 37 (2003): Über die Fahrkorbtür-Verriegelung außerhalb der Entriegelungszone.</t>
+        </is>
+      </c>
       <c r="K53" s="3" t="n"/>
       <c r="L53" s="3" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>53</v>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>5.9.4, 5.12.1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Auslegung des Triebwerks und der Bremse</t>
+          <t>Schachttüren und Fahrkorbtüren</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>Vorhandensein der Fahrkorbtür(en)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>I/D</t>
-        </is>
-      </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -3144,12 +3278,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>MF-M08</t>
+          <t>MF-T06</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Unzureichende elektromechanische Bremse (Einkreisbremse, keine Überwachung)</t>
+          <t>Fahrkorb ohne Abschlusstür oder ohne Schließkantensicherung</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3162,90 +3296,98 @@
       <c r="L54" s="3" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>5.9.5</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Schutz gegen freien Fall, Übergeschwindigkeit und Absinken bei Hydraulikaufzügen</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>Hoch</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>I/D</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>Kurzfristig</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>MF-M13</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>Unzureichende Hydraulikeinrichtungen (Absperrventil, Rohrbruchsicherung, Absinken)</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>voll</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="inlineStr"/>
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>neu 2019</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Schachttüren und Fahrkorbtüren</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Fahrkorbtürdrossel, wo die Verriegelungseinrichtung der Schachttür zugänglich ist</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Mittel</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>Fahrkorbtürdrossel bei zugänglicher Schachttürverriegelung wird nicht erhoben.</t>
+        </is>
+      </c>
       <c r="K55" s="3" t="n"/>
       <c r="L55" s="3" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>55</v>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>5.10.1</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Gegengewicht oder Ausgleichsgewicht durch Seile statt Schienen geführt</t>
+          <t>Fahrkorb, Gegengewicht und Ausgleichsgewicht</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Mittel</t>
+          <t>Verhältnis von Nutzfläche zur Nennlast</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>I/D-E, II/D</t>
+          <t>Niedrig</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
+          <t>Langfristig oder im Rahmen einer Modernisierung der betroffenen Komponente</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>MF-S04</t>
+          <t>MF-K06</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Führungsschienen nicht aus Stahl</t>
+          <t>Fehlende Kennzeichnung der Nennlast, unpassende Nutzfläche oder fehlende Überlastkontrolle</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3258,29 +3400,31 @@
       <c r="L56" s="3" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n">
-        <v>56</v>
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>5.10.2</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Puffer für Fahrkorb und Gegengewicht</t>
+          <t>Fahrkorb, Gegengewicht und Ausgleichsgewicht</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
+          <t>Fahrkorbschürze</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>II/C</t>
-        </is>
-      </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -3288,12 +3432,12 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>MF-G06</t>
+          <t>MF-K04</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Fehlende, beschädigte oder ungeeignete Puffer</t>
+          <t>Unzureichende Fahrkorbtürschürze</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3306,42 +3450,44 @@
       <c r="L57" s="3" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>57</v>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>5.10.3</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Notendschalter</t>
+          <t>Fahrkorb, Gegengewicht und Ausgleichsgewicht</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Hoch</t>
+          <t>Verriegelung der Notklappe auf dem Fahrkorb</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>III/B</t>
+          <t>Mittel</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Kurzfristig</t>
+          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>MF-M21</t>
+          <t>MF-F07</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Fehlende oder unwirksame Notendschalter</t>
+          <t>Nicht tragfähiges Fahrkorbdach oder unüberwachte Dachklappe</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3349,90 +3495,86 @@
           <t>voll</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>Ergänzt 04.09.2026 (EN 81-20 5.12.2).</t>
-        </is>
-      </c>
+      <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="3" t="n"/>
       <c r="L58" s="3" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>5.11.1</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>Abstand zwischen Fahrkorb und der dem Zugang gegenüber-liegenden Schachtwand</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>Hoch</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>I/D</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>Kurzfristig</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>MF-F01</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>Fehlende oder unzureichende Absturzsicherung auf dem Fahrkorbdach</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>teilweise</t>
-        </is>
-      </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t>MF erhebt den Abstand an der Fahrkorbdachkante (Absturzsicherung).</t>
-        </is>
-      </c>
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Fahrkorb, Gegengewicht und Ausgleichsgewicht</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Festigkeit des Fahrkorbdachs und der Notklappe</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Niedrig</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Langfristig oder im Rahmen einer Modernisierung der betroffenen Komponente</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>MF-F07</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Nicht tragfähiges Fahrkorbdach oder unüberwachte Dachklappe</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr"/>
       <c r="K59" s="3" t="n"/>
       <c r="L59" s="3" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>59</v>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>5.11.2</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Abstand zwischen Fahrkorbschwelle und Schachttür</t>
+          <t>Fahrkorb, Gegengewicht und Ausgleichsgewicht</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>Schutz gegen Absturz vom Fahrkorbdach (Umwehrung)</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>I/D</t>
-        </is>
-      </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -3440,12 +3582,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>MF-K05</t>
+          <t>MF-F01</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Zu großer Abstand zwischen Fahrkorbschwelle und Schachtwand</t>
+          <t>Fehlende oder unzureichende Absturzsicherung auf dem Fahrkorbdach</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3458,42 +3600,44 @@
       <c r="L60" s="3" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
-        <v>60</v>
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>5.12.2</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Einrichtung für den Notbetrieb und die Personenbefreiung</t>
+          <t>Fahrkorb, Gegengewicht und Ausgleichsgewicht</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Extrem</t>
+          <t>Fahrkorbbelüftung</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>I/B, I/D</t>
+          <t>Mittel</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Sofort, Aufzug muss stillgelegt werden</t>
+          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>MF-M15</t>
+          <t>MF-K07</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Fehlende oder unzureichende Einrichtung für Notbetrieb und Personenbefreiung</t>
+          <t>Unzureichende Lüftung des Fahrkorbs</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3506,29 +3650,31 @@
       <c r="L61" s="3" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>61</v>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>5.12.3</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Absperrventil am Hydraulikaggregat</t>
+          <t>Fahrkorb, Gegengewicht und Ausgleichsgewicht</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>Normale Beleuchtung im Fahrkorb</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
           <t>Mittel</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>III/C-D</t>
-        </is>
-      </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
@@ -3536,12 +3682,12 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>MF-M13</t>
+          <t>MF-K15</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Unzureichende Hydraulikeinrichtungen (Absperrventil, Rohrbruchsicherung, Absinken)</t>
+          <t>Unzureichende Beleuchtung im Fahrkorb (Normalbetrieb)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3549,47 +3695,53 @@
           <t>voll</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>Nr. 45 (2003): Ergänzt 04.09.2026 (EN 81-20 5.4.10.1 bis 5.4.10.3: mind. 100 Lux an den Befehlsgebern und 1 m über dem Boden bis 100 mm an die Wände).</t>
+        </is>
+      </c>
       <c r="K62" s="3" t="n"/>
       <c r="L62" s="3" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n">
-        <v>62</v>
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>5.12.4</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Zwei unabhängige Schütze im Antriebsstromkreis</t>
+          <t>Fahrkorb, Gegengewicht und Ausgleichsgewicht</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Hoch</t>
+          <t>Notbeleuchtung im Fahrkorb</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>I/D</t>
+          <t>Mittel</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Kurzfristig</t>
+          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>MF-M10</t>
+          <t>MF-K02</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Fehlende unabhängige Fahrschütze / Abschaltwege</t>
+          <t>Fehlende oder unzulängliche Notbeleuchtung im Fahrkorb</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -3602,42 +3754,44 @@
       <c r="L63" s="3" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>63</v>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>5.12.5</t>
+          <t>neu 2019</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Schlaffseil-/Schlaffketteneinrichtung</t>
+          <t>Fahrkorb, Gegengewicht und Ausgleichsgewicht</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Hoch</t>
+          <t>Notbeleuchtung auf dem Fahrkorbdach</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>II/C-D</t>
+          <t>Niedrig</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Kurzfristig</t>
+          <t>Langfristig oder im Rahmen einer Modernisierung der betroffenen Komponente</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>MF-S05</t>
+          <t>MF-F08</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Fehlende oder ungeprüfte Fangvorrichtung, Geschwindigkeitsbegrenzer oder Schlaffseilsicherung</t>
+          <t>Fehlende Notbeleuchtung auf dem Fahrkorbdach</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3645,47 +3799,53 @@
           <t>voll</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Im MF-Fragebogen bereits enthalten (Frage 9.12), obwohl in der Ausgabe 2003 nicht abgedeckt.</t>
+        </is>
+      </c>
       <c r="K64" s="3" t="n"/>
       <c r="L64" s="3" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n">
-        <v>64</v>
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>5.10</t>
+        </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>5.12.6</t>
+          <t>73</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Laufzeitüberwachung des Antriebs</t>
+          <t>Fahrkorb, Gegengewicht und Ausgleichsgewicht</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Mittel</t>
+          <t>Kontrolle der Beladung, um einen Start des Fahrkorbs bei Überladung zu verhindern</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>III/C-D</t>
+          <t>Niedrig</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
+          <t>Langfristig oder im Rahmen einer Modernisierung der betroffenen Komponente</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>MF-M11</t>
+          <t>MF-K06</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Fehlende Laufzeitüberwachung des Antriebs</t>
+          <t>Fehlende Kennzeichnung der Nennlast, unpassende Nutzfläche oder fehlende Überlastkontrolle</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3698,29 +3858,31 @@
       <c r="L65" s="3" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>65</v>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>5.11</t>
+        </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>5.12.7</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Einrichtung gegen Absinken des Kolbens</t>
+          <t>Fahrkorb, Gegengewicht und Ausgleichsgewicht</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>Fernnotrufeinrichtung mit Zweiwegeverständigung</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>II/C-D</t>
-        </is>
-      </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -3728,12 +3890,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>MF-M13</t>
+          <t>MF-K01</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Unzureichende Hydraulikeinrichtungen (Absperrventil, Rohrbruchsicherung, Absinken)</t>
+          <t>Fehlende oder unzulängliche Notrufeinrichtung im Fahrkorb</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3746,43 +3908,44 @@
       <c r="L66" s="3" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n">
-        <v>66</v>
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>5.13.1</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Schutz gegen elektrischen Schlag und Kennzeichnung elektrischer Einrichtungen</t>
+          <t>Aufhängungsmittel, Ausgleichsmittel, Schutz gegen freien Fall, Übergeschwindigkeit, unbeabsichtigte Bewegung und Absinken des Fahrkorbs</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Hoch</t>
+          <t>Schutz gegen Verletzungen an Treibscheiben, Seilrollen oder Kettenrädern</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>I/D</t>
+          <t>Mittel</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Kurzfristig</t>
+          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>MF-M02, MF-M17</t>
+          <t>MF-M03</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Unzureichender Schutz gegen elektrischen Schlag (offene Schalttafel, offene Kontakte, fehlende Berührungssicherheit)
-Fehlende Kennzeichnung elektrischer Einrichtungen, Stromlaufplan, Beschilderung und Betriebsanleitung</t>
+          <t>Fehlender oder unzureichender Schutz an drehenden Teilen (Treibscheibe, Umlenkrollen, Begrenzer)</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3795,29 +3958,31 @@
       <c r="L67" s="3" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
-        <v>67</v>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>5.13.2</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Schutz des Triebwerksmotors gegen Überhitzen</t>
+          <t>Aufhängungsmittel, Ausgleichsmittel, Schutz gegen freien Fall, Übergeschwindigkeit, unbeabsichtigte Bewegung und Absinken des Fahrkorbs</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>Schutz gegen das Herausspringen von Seilen oder Ketten</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
           <t>Mittel</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>II/D</t>
-        </is>
-      </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
@@ -3825,12 +3990,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>MF-M09</t>
+          <t>MF-M03</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Fehlender Schutz des Antriebsmotors gegen Überhitzen</t>
+          <t>Fehlender oder unzureichender Schutz an drehenden Teilen (Treibscheibe, Umlenkrollen, Begrenzer)</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3843,42 +4008,44 @@
       <c r="L68" s="3" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n">
-        <v>68</v>
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>5.13.3</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Abschließbarer Hauptschalter</t>
+          <t>Aufhängungsmittel, Ausgleichsmittel, Schutz gegen freien Fall, Übergeschwindigkeit, unbeabsichtigte Bewegung und Absinken des Fahrkorbs</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Hoch</t>
+          <t>Schutz gegen das Eindringen von Fremdkörpern zwischen Seil/Kette und Scheibe</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>I/D</t>
+          <t>Niedrig</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Kurzfristig</t>
+          <t>Langfristig oder im Rahmen einer Modernisierung der betroffenen Komponente</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>MF-M07</t>
+          <t>MF-M03</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Fehlender, nicht abschließbarer oder nicht gekennzeichneter Hauptschalter</t>
+          <t>Fehlender oder unzureichender Schutz an drehenden Teilen (Treibscheibe, Umlenkrollen, Begrenzer)</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3891,42 +4058,45 @@
       <c r="L69" s="3" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
-        <v>69</v>
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>5.14.1</t>
+          <t>50, 54</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Schutz gegen Phasenumkehr und Phasenausfall</t>
+          <t>Aufhängungsmittel, Ausgleichsmittel, Schutz gegen freien Fall, Übergeschwindigkeit, unbeabsichtigte Bewegung und Absinken des Fahrkorbs</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Mittel</t>
+          <t>Schutz gegen freien Fall und Abwärtsbewegung mit überhöhter Geschwindigkeit</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>II/D</t>
+          <t>Hoch</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
+          <t>Kurzfristig</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>MF-M12</t>
+          <t>MF-S05, MF-M13</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Fehlender Schutz gegen Phasenumkehr / Phasenausfall</t>
+          <t>Fehlende oder ungeprüfte Fangvorrichtung, Geschwindigkeitsbegrenzer oder Schlaffseilsicherung
+Unzureichende Hydraulikeinrichtungen (Absperrventil, Rohrbruchsicherung, Absinken)</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3939,43 +4109,44 @@
       <c r="L70" s="3" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="n">
-        <v>70</v>
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>5.14.2</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Inspektionssteuerung und Not-Halt auf dem Fahrkorbdach</t>
+          <t>Aufhängungsmittel, Ausgleichsmittel, Schutz gegen freien Fall, Übergeschwindigkeit, unbeabsichtigte Bewegung und Absinken des Fahrkorbs</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Extrem</t>
+          <t>Schutz gegen unkontrollierte Aufwärtsbewegung (Treibscheibenaufzug mit Gegengewicht)</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>I/C</t>
+          <t>Mittel</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Sofort, Aufzug muss stillgelegt werden</t>
+          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>MF-F05, MF-F06</t>
+          <t>MF-K13</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Fehlende oder unzulängliche Inspektionssteuerung auf dem Fahrkorbdach
-Fehlender oder unwirksamer Not-Halt auf dem Fahrkorbdach</t>
+          <t>Fehlender Schutz gegen Übergeschwindigkeit aufwärts / Sturz nach oben</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -3988,29 +4159,31 @@
       <c r="L71" s="3" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
-        <v>71</v>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>5.14.3</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Notrufeinrichtung im Fahrkorb (Zweiwege-System nach EN 81-28)</t>
+          <t>Aufhängungsmittel, Ausgleichsmittel, Schutz gegen freien Fall, Übergeschwindigkeit, unbeabsichtigte Bewegung und Absinken des Fahrkorbs</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>Schutz gegen unbeabsichtigte Bewegung des Fahrkorbs bei offenen Türen (UCM)</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>I/D, II/C</t>
-        </is>
-      </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -4018,12 +4191,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>MF-K01</t>
+          <t>MF-M08</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Fehlende oder unzulängliche Notrufeinrichtung im Fahrkorb</t>
+          <t>Unzureichende elektromechanische Bremse (Einkreisbremse, keine Überwachung)</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -4036,29 +4209,31 @@
       <c r="L72" s="3" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="n">
-        <v>72</v>
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>5.14.4</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Sprechverbindung Triebwerksraum – Fahrkorb (Förderhöhe &gt; 30 m)</t>
+          <t>Aufhängungsmittel, Ausgleichsmittel, Schutz gegen freien Fall, Übergeschwindigkeit, unbeabsichtigte Bewegung und Absinken des Fahrkorbs</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
+          <t>Schutz gegen Absinken bei Hydraulikaufzügen (oder Klemmvorrichtung)</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
           <t>Hoch</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>I/D</t>
-        </is>
-      </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
           <t>Kurzfristig</t>
@@ -4066,12 +4241,12 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>MF-M18</t>
+          <t>MF-M13</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>Fehlende oder unzulängliche Sprechverbindung zwischen Fahrkorb und Triebwerksraum</t>
+          <t>Unzureichende Hydraulikeinrichtungen (Absperrventil, Rohrbruchsicherung, Absinken)</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -4084,29 +4259,31 @@
       <c r="L73" s="3" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
-        <v>73</v>
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>5.14.5</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Kontrolle der Beladung des Fahrkorbs (Überlastkontrolle)</t>
+          <t>Aufhängungsmittel, Ausgleichsmittel, Schutz gegen freien Fall, Übergeschwindigkeit, unbeabsichtigte Bewegung und Absinken des Fahrkorbs</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>Schlaffseilschalter am Begrenzerseil für Übergeschwindigkeit</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>Mittel</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>I/D-E, II/D</t>
-        </is>
-      </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
@@ -4114,12 +4291,12 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>MF-K06</t>
+          <t>MF-S05</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Fehlende Kennzeichnung der Nennlast, unpassende Nutzfläche oder fehlende Überlastkontrolle</t>
+          <t>Fehlende oder ungeprüfte Fangvorrichtung, Geschwindigkeitsbegrenzer oder Schlaffseilsicherung</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -4132,43 +4309,44 @@
       <c r="L74" s="3" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="n">
-        <v>74</v>
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Hinweise, Kennzeichnungen und Bedienungsanleitung</t>
+          <t>Aufhängungsmittel, Ausgleichsmittel, Schutz gegen freien Fall, Übergeschwindigkeit, unbeabsichtigte Bewegung und Absinken des Fahrkorbs</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Hoch</t>
+          <t>Sicherheitseinrichtung gegen Schlaffseil oder Schlaffkette</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>I/D</t>
+          <t>Mittel</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Kurzfristig</t>
+          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>MF-M17, MF-D02</t>
+          <t>MF-S05</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>Fehlende Kennzeichnung elektrischer Einrichtungen, Stromlaufplan, Beschilderung und Betriebsanleitung
-Keine oder unpassende Notbefreiungsanleitung</t>
+          <t>Fehlende oder ungeprüfte Fangvorrichtung, Geschwindigkeitsbegrenzer oder Schlaffseilsicherung</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -4180,10 +4358,1034 @@
       <c r="K75" s="3" t="n"/>
       <c r="L75" s="3" t="n"/>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Führungsschienen, Puffer und Notendschalter</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Führungen für Gegengewicht oder Ausgleichsgewicht</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Niedrig</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Langfristig oder im Rahmen einer Modernisierung der betroffenen Komponente</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>MF-S04</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Führungsschienen nicht aus Stahl</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="3" t="n"/>
+      <c r="L76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Führungsschienen, Puffer und Notendschalter</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Fahrkorb- und Gegengewichtspuffer</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>Kurzfristig</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>MF-G06</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>Fehlende, beschädigte oder ungeeignete Puffer</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr"/>
+      <c r="K77" s="3" t="n"/>
+      <c r="L77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Führungsschienen, Puffer und Notendschalter</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Notendschalter</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Mittel</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>MF-M21</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Fehlende oder unwirksame Notendschalter</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Nr. 57 (2003): Ergänzt 04.09.2026 (EN 81-20 5.12.2).</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="n"/>
+      <c r="L78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>neu 2019</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Triebwerk</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Mindestens zwei unabhängige Bremssätze</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>Kurzfristig</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>MF-M08</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>Unzureichende elektromechanische Bremse (Einkreisbremse, keine Überwachung)</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>MF-M08 erhebt die Zweikreisbremse (Frage 6.2) und ihre Überwachung.</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="n"/>
+      <c r="L79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Triebwerk</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Notbetriebssystem</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Kurzfristig</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>MF-M15</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Fehlende oder unzureichende Einrichtung für Notbetrieb und Personenbefreiung</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="3" t="n"/>
+      <c r="L80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Triebwerk</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Mittel zum Stillsetzen des Antriebs und Überwachung seines Stillstands</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>Kurzfristig</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>MF-M10</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>Fehlende unabhängige Fahrschütze / Abschaltwege</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr"/>
+      <c r="K81" s="3" t="n"/>
+      <c r="L81" s="3" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Triebwerk</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Motorlaufzeitüberwachung</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Niedrig</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Langfristig oder im Rahmen einer Modernisierung der betroffenen Komponente</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>MF-M11</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Fehlende Laufzeitüberwachung des Antriebs</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="3" t="n"/>
+      <c r="L82" s="3" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Triebwerk</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>Absperrventil (Hydraulikaufzüge)</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Niedrig</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>Langfristig oder im Rahmen einer Modernisierung der betroffenen Komponente</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>MF-M13</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>Unzureichende Hydraulikeinrichtungen (Absperrventil, Rohrbruchsicherung, Absinken)</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr"/>
+      <c r="K83" s="3" t="n"/>
+      <c r="L83" s="3" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Triebwerk</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Kolbenabsinkvorrichtung bei Hydraulikaufzügen</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Mittel</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>MF-M13</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Unzureichende Hydraulikeinrichtungen (Absperrventil, Rohrbruchsicherung, Absinken)</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="3" t="n"/>
+      <c r="L84" s="3" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Elektrische Installationen und Einrichtungen</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>Schutz gegen elektrischen Schlag (direktes Berühren)</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>Kurzfristig</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>MF-M02, MF-M17</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>Unzureichender Schutz gegen elektrischen Schlag (offene Schalttafel, offene Kontakte, fehlende Berührungssicherheit)
+Fehlende Kennzeichnung elektrischer Einrichtungen, Stromlaufplan, Beschilderung und Betriebsanleitung</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr"/>
+      <c r="K85" s="3" t="n"/>
+      <c r="L85" s="3" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Elektrische Installationen und Einrichtungen</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Kennzeichnung von Anschlussklemmen, die nach dem Ausschalten des Hauptschalters unter Strom bleiben</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Kurzfristig</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>MF-M02, MF-M17</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Unzureichender Schutz gegen elektrischen Schlag (offene Schalttafel, offene Kontakte, fehlende Berührungssicherheit)
+Fehlende Kennzeichnung elektrischer Einrichtungen, Stromlaufplan, Beschilderung und Betriebsanleitung</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="3" t="n"/>
+      <c r="L86" s="3" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Elektrische Installationen und Einrichtungen</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Schutz gegen Überhitzung des Triebwerksmotors</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Niedrig</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>Langfristig oder im Rahmen einer Modernisierung der betroffenen Komponente</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>MF-M09</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>Fehlender Schutz des Antriebsmotors gegen Überhitzen</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr"/>
+      <c r="K87" s="3" t="n"/>
+      <c r="L87" s="3" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Elektrische Installationen und Einrichtungen</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Abschließbarer Hauptschalter</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Kurzfristig</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>MF-M07</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Fehlender, nicht abschließbarer oder nicht gekennzeichneter Hauptschalter</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="3" t="n"/>
+      <c r="L88" s="3" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>neu 2019</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Elektrische Installationen und Einrichtungen</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Bremseinrichtung an der Anlage am Aufstellungsort von Triebwerk und Steuerung</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>Niedrig</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>Langfristig oder im Rahmen einer Modernisierung der betroffenen Komponente</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>Bremseinrichtung am Aufstellungsort von Triebwerk und Steuerung wird nicht gesondert erhoben.</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="n"/>
+      <c r="L89" s="3" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>neu 2019</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Schutz gegen elektrische Fehler, Steuerungen, Vorrechte</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Erdfehlerschutz in Stromkreisen mit elektrischen Sicherheitseinrichtungen und in Bremsen-/Abwärtsventil-Schaltkreisen</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>Mittel</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>Erdfehlerschutz in Sicherheits- und Bremsstromkreisen wird nicht erhoben.</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="n"/>
+      <c r="L90" s="3" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Schutz gegen elektrische Fehler, Steuerungen, Vorrechte</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Schutz gegen Stromphasenumkehr</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>Niedrig</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>Langfristig oder im Rahmen einer Modernisierung der betroffenen Komponente</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>MF-M12</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>Fehlender Schutz gegen Phasenumkehr / Phasenausfall</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr"/>
+      <c r="K91" s="3" t="n"/>
+      <c r="L91" s="3" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Schutz gegen elektrische Fehler, Steuerungen, Vorrechte</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Nachregulierungs- und Anhaltegenauigkeit des Fahrkorbs</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Kurzfristig</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>MF-K03</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Unzureichende Haltegenauigkeit / Stufenbildung an den Haltestellen</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="3" t="n"/>
+      <c r="L92" s="3" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Schutz gegen elektrische Fehler, Steuerungen, Vorrechte</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Inspektionssteuerung und Bremseinrichtung auf dem Fahrkorbdach</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>Kurzfristig</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>MF-F05, MF-F06</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>Fehlende oder unzulängliche Inspektionssteuerung auf dem Fahrkorbdach
+Fehlender oder unwirksamer Not-Halt auf dem Fahrkorbdach</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr"/>
+      <c r="K93" s="3" t="n"/>
+      <c r="L93" s="3" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>neu 2019</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Schutz gegen elektrische Fehler, Steuerungen, Vorrechte</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Inspektionskontrolle in der Schachtgrube</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>Niedrig</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>Langfristig oder im Rahmen einer Modernisierung der betroffenen Komponente</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>MF-G03</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>Fehlender Not-Halt oder fehlende Inspektionssteuerung in der Schachtgrube</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>teilweise</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>MF-G03 erhebt die Inspektionssteuerung in der Schachtgrube (Frage 11.5) zusammen mit dem Not-Halt.</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="n"/>
+      <c r="L94" s="3" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Hinweise, Kennzeichnungen und Betriebsanleitungen</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Hinweise zum sicheren Betrieb und zur Instandhaltung des Aufzugs</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>Mittel</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>Mittelfristig oder im Rahmen einer umfangreichen Modernisierung</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>MF-M17, MF-D02</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>Fehlende Kennzeichnung elektrischer Einrichtungen, Stromlaufplan, Beschilderung und Betriebsanleitung
+Keine oder unpassende Notbefreiungsanleitung</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>voll</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr"/>
+      <c r="K95" s="3" t="n"/>
+      <c r="L95" s="3" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L75"/>
+  <autoFilter ref="A1:L95"/>
   <dataValidations count="1">
-    <dataValidation sqref="K2:K75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,Ändern"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4197,7 +5399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -4206,14 +5408,14 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>EN 81-80 als Sicht auf den mehrfragigen Katalog (81-20-mf-2026.3)</t>
+          <t>EN 81-80 als Sicht auf den mehrfragigen Katalog (81-20-mf-2026.10)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Quelle: DIN EN 81-80:2004-02, Tabelle 1 sowie Anhang A (Tabellen A.1 und A.2)</t>
+          <t>Quelle: DIN EN 81-80:2019-11, Anhang A (normativ), Tabelle A.1, sowie Abschnitt 5.4 mit Tabelle 4 (Prioritäten und Zeitplan)</t>
         </is>
       </c>
     </row>
@@ -4223,7 +5425,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Der eingefrorene GBU-Typ „vereinfacht (EN 81-80)" wird nicht durch einen zweiten Fragebogen ersetzt: Eine Bestandsanlage wird einmal nach EN 81-20 (mehrfragig) erhoben, der Bericht weist den Nachrüstbedarf nach EN 81-80 zusätzlich mit Nummer, Abschnitt und Priorität der Norm aus.</t>
+          <t>Der eingefrorene GBU-Typ „vereinfacht (EN 81-80)" wird nicht durch einen zweiten Fragebogen ersetzt: Eine Bestandsanlage wird einmal nach EN 81-20 (mehrfragig) erhoben, der Bericht weist den Nachrüstbedarf nach EN 81-80 zusätzlich mit Nummer und Priorität der Norm aus.</t>
         </is>
       </c>
     </row>
@@ -4233,21 +5435,21 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>71 der 74 Gefährdungssituationen sind vollständig abgedeckt, 3 teilweise, 0 gar nicht (Spalten rot hinterlegt).</t>
+          <t>81 der 94 Prüfpunkte sind vollständig abgedeckt, 6 teilweise, 7 gar nicht (Zeilen rot hinterlegt).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lücken im MF-Katalog: </t>
+          <t>Lücken im MF-Katalog: Nr. 1.5 Erdbebensicherheit (EN 81-77), Nr. 2.19 Abstand zwischen den Führungskanten von Fahrkorbtür und Schachttür, Nr. 4.4 Festigkeit von Fahrkorbtüren, Nr. 4.11 Begrenzung des Kraftaufwands (150 N) beim Schließen anderer als automatisch kraftbetätigter Schiebetüren, Nr. 4.21 Fahrkorbtürdrossel, wo die Verriegelungseinrichtung der Schachttür zugänglich ist, Nr. 9.5 Bremseinrichtung an der Anlage am Aufstellungsort von Triebwerk und Steuerung, Nr. 10.1 Erdfehlerschutz in Stromkreisen mit elektrischen Sicherheitseinrichtungen und in Bremsen-/Abwärtsventil-Schaltkreisen</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Teilweise: Nr. 25 Durchbrochene Schacht- und Fahrkorbtüren (Gittertüren), Nr. 33 Durchbrochene Schachtwand in der Nähe der Türverriegelung, Nr. 58 Abstand zwischen Fahrkorb und der dem Zugang gegenüber-liegenden Schachtwand</t>
+          <t>Teilweise: Nr. 1.3 Feuerwehraufzug (EN 81-72), Nr. 2.4 Zugang zu den Verriegelungseinrichtungen der Schachttür bei durchbrochener Umwehrung, Nr. 2.17 Horizontaler Abstand zwischen innerer Schachtwand und Türschwelle bzw. Türrahmen des Fahrkorbs, Nr. 4.1 Vollwandige Schachttüren, Nr. 4.2 Vollwandige Fahrkorbtüren, Nr. 10.5 Inspektionskontrolle in der Schachtgrube</t>
         </is>
       </c>
     </row>
@@ -4257,7 +5459,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Priorität nach Tabelle A.2 aus dem Risikoprofil A.1 abgeleitet (Schwere/Häufigkeit); erscheint eine Nummer dort mehrfach, gilt die höhere Stufe. Die Nummern 2, 4 und 5 sind in A.1 nicht enthalten (besondere Anforderungen nach 5.1.5) und deshalb nicht eingestuft.</t>
+          <t>Die Prioritätsstufe steht seit der Ausgabe 2019 direkt in der Prüfliste; die frühere Herleitung über Risikoprofil (A.1) und Prioritätstabelle (A.2) entfällt. Fünf Punkte sind ohne Stufe: sie verweisen auf eine eigene Norm der Reihe EN 81 (81-72 Feuerwehraufzug, 81-73 Brandfall, 81-77 Erdbeben, 81-82 Barrierefreiheit, CEN/TS 81-83 Vandalismus).</t>
         </is>
       </c>
     </row>
@@ -4267,7 +5469,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Gelbe Spalten ausfüllen: „Zuordnung OK?" = OK/Ändern, Korrektur frei.</t>
+          <t>Spalte „Nr. 2003" ist die Nummer der zurückgezogenen Ausgabe 2004-02; „neu 2019" kennzeichnet die elf Punkte, die es dort nicht gab.</t>
         </is>
       </c>
     </row>
@@ -4275,9 +5477,19 @@
       <c r="A13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Stand der Gegenlesung: 2026-09-04 – Zuordnung und Deckungsangaben fachlich gegengelesen; die Bemerkungen zu den teilweise abgedeckten Punkten (Nr. 25, 33, 58) sind bestätigt.</t>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Gelbe Spalten ausfüllen: „Zuordnung OK?" = OK/Ändern, Korrektur frei.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Stand der Gegenlesung: 2026-09-04 – Zuordnung und Deckungsangaben der Ausgabe 2004 fachlich gegengelesen und mit der Spalte „Nr. in EN 81-80:2003" auf die Nummerierung der Ausgabe 2019 gehoben. Noch nicht gegengelesen: die elf neuen Punkte und die 37 geänderten Prioritätsstufen.</t>
         </is>
       </c>
     </row>
